--- a/outbreaks/results/dxri_wo_COVID_20250212.xlsx
+++ b/outbreaks/results/dxri_wo_COVID_20250212.xlsx
@@ -622,7 +622,7 @@
         <v>28</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -678,7 +678,7 @@
         <v>111</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1206,7 +1206,7 @@
         <v>10.48689138576779</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -1262,7 +1262,7 @@
         <v>41.57303370786517</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12">
@@ -1816,10 +1816,10 @@
         <v>10.48689138576779</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I9">
-        <v>5.708259209472454</v>
+        <v>19.99397349518674</v>
       </c>
     </row>
     <row r="10">
@@ -1878,10 +1878,10 @@
         <v>41.57303370786517</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I11">
-        <v>23.92139960648016</v>
+        <v>38.20711389219444</v>
       </c>
     </row>
     <row r="12">
